--- a/public/template/import-products-template.xlsx
+++ b/public/template/import-products-template.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19680" windowHeight="17565"/>
+    <workbookView windowWidth="20010" windowHeight="17580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>Nama</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Satuan</t>
   </si>
   <si>
-    <t>Barcode (Opsional)</t>
+    <t>Barcode</t>
   </si>
   <si>
     <t>Stok</t>
@@ -56,7 +56,7 @@
     <t>Tipe Stok</t>
   </si>
   <si>
-    <t>Deskripsi (Opsional)</t>
+    <t>Deskripsi</t>
   </si>
   <si>
     <t>Keterangan</t>
@@ -92,6 +92,9 @@
   <si>
     <t>Catatan
 Nilai Jika tidak diisi:  T</t>
+  </si>
+  <si>
+    <t>Opsional</t>
   </si>
 </sst>
 </file>
@@ -116,7 +119,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -817,7 +819,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -846,9 +848,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1376,9 +1375,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="12.8571428571429" customWidth="1"/>
+    <col min="6" max="6" width="14.1428571428571" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
     <col min="13" max="13" width="18.8571428571429" customWidth="1"/>
     <col min="14" max="14" width="19.2857142857143" customWidth="1"/>
   </cols>
@@ -1451,16 +1454,16 @@
       <c r="N6" s="9"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
     </row>
     <row r="10" ht="15.75" spans="1:14">
       <c r="M10" s="1"/>
@@ -1499,6 +1502,22 @@
     <row r="15" spans="1:14">
       <c r="M15" s="8"/>
       <c r="N15" s="9"/>
+    </row>
+    <row r="17" spans="13:14">
+      <c r="M17" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="13:14">
+      <c r="M18" t="s">
+        <v>9</v>
+      </c>
+      <c r="N18" t="s">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/public/template/import-products-template.xlsx
+++ b/public/template/import-products-template.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19680" windowHeight="17565"/>
+    <workbookView windowWidth="19200" windowHeight="17580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
     <t>Satuan</t>
   </si>
   <si>
-    <t>Barcode (Opsional)</t>
+    <t>Barcode</t>
   </si>
   <si>
     <t>Stok</t>
@@ -56,7 +56,7 @@
     <t>Tipe Stok</t>
   </si>
   <si>
-    <t>Deskripsi (Opsional)</t>
+    <t>Deskripsi</t>
   </si>
   <si>
     <t>Keterangan</t>
@@ -116,7 +116,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -817,7 +816,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -846,9 +845,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1451,16 +1447,16 @@
       <c r="N6" s="9"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
     </row>
     <row r="10" ht="15.75" spans="1:14">
       <c r="M10" s="1"/>
